--- a/src/test/resources/VitigerTestData.xlsx
+++ b/src/test/resources/VitigerTestData.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6920"/>
+    <workbookView windowWidth="18350" windowHeight="6320" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Orgdata" sheetId="1" r:id="rId1"/>
+    <sheet name="orgdata" sheetId="1" r:id="rId1"/>
     <sheet name="Condata" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
